--- a/InputData/trans/MPoEFUbVT/Max Perc of Each Fuel Usable by Veh Tech.xlsx
+++ b/InputData/trans/MPoEFUbVT/Max Perc of Each Fuel Usable by Veh Tech.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\MPoEFUbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\trans\MPoEFUbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FBF57E-9E0A-4861-96FF-003F2EEA3BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{036B868E-71DA-4EB8-BD7B-BEB6F04D77CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="1110" windowWidth="23520" windowHeight="15450" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
